--- a/benchmark/RAG/figure/relations-figure.xlsx
+++ b/benchmark/RAG/figure/relations-figure.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="55">
   <si>
     <t>Openviking实验数据（agentic-learned)</t>
   </si>
@@ -61,6 +61,12 @@
     <t>迭代次数</t>
   </si>
   <si>
+    <t>search次数</t>
+  </si>
+  <si>
+    <t>read次数</t>
+  </si>
+  <si>
     <t>bot版本；0.2.10开发版；max_iterations=50（默认）</t>
   </si>
   <si>
@@ -70,94 +76,73 @@
     <t>FinanceBench</t>
   </si>
   <si>
-    <t>67s</t>
-  </si>
-  <si>
-    <t>68673+1934=70,607‬</t>
+    <t>27639+2021=29,660/query</t>
   </si>
   <si>
     <t>QASPER</t>
   </si>
   <si>
+    <t>20008+1853=21,861‬/query</t>
+  </si>
+  <si>
+    <t>SyllabusQA</t>
+  </si>
+  <si>
+    <t>21023+1800=22,823‬/query</t>
+  </si>
+  <si>
+    <t>LocoMo</t>
+  </si>
+  <si>
+    <t>NaturalQuestions (NQ)</t>
+  </si>
+  <si>
+    <t>48s</t>
+  </si>
+  <si>
+    <t>18309+1361=19,670/query</t>
+  </si>
+  <si>
+    <t>HotpotQA</t>
+  </si>
+  <si>
+    <t>45s</t>
+  </si>
+  <si>
+    <t>22974+1271=24,245‬/query</t>
+  </si>
+  <si>
+    <t>Openviking实验数据（agentic-unlearned）</t>
+  </si>
+  <si>
+    <t>77s</t>
+  </si>
+  <si>
+    <t>37490+2275=39,765/query</t>
+  </si>
+  <si>
+    <t>70s</t>
+  </si>
+  <si>
+    <t>25212+1807=27,019/query</t>
+  </si>
+  <si>
+    <t>55.28s</t>
+  </si>
+  <si>
+    <t>25860+1809=27,669‬/query</t>
+  </si>
+  <si>
+    <t>50s</t>
+  </si>
+  <si>
+    <t>19118+1401=20,519‬/query</t>
+  </si>
+  <si>
     <t>47s</t>
   </si>
   <si>
-    <t>37914+1624=39,538</t>
-  </si>
-  <si>
-    <t>SyllabusQA</t>
-  </si>
-  <si>
-    <t>62.02s</t>
-  </si>
-  <si>
-    <t>40230+1777=42,007‬</t>
-  </si>
-  <si>
-    <t>LocoMo</t>
-  </si>
-  <si>
-    <t>51s</t>
-  </si>
-  <si>
-    <t>37587+1403=38,990/query</t>
-  </si>
-  <si>
-    <t>NaturalQuestions (NQ)</t>
-  </si>
-  <si>
-    <t>42s</t>
-  </si>
-  <si>
-    <t>33105+1191=34,296/query</t>
-  </si>
-  <si>
-    <t>HotpotQA</t>
-  </si>
-  <si>
-    <t>62s</t>
-  </si>
-  <si>
-    <t>52260+1427=53687/query</t>
-  </si>
-  <si>
-    <t>Openviking实验数据（agentic-unlearned）</t>
-  </si>
-  <si>
-    <t>70s</t>
-  </si>
-  <si>
-    <t>91597+1947=93,544/query</t>
-  </si>
-  <si>
-    <t>53s</t>
-  </si>
-  <si>
-    <t>46058+1640=47,698/query</t>
-  </si>
-  <si>
-    <t>62.44s</t>
-  </si>
-  <si>
-    <t>47608+1785=49,393/query</t>
-  </si>
-  <si>
-    <t>58s</t>
-  </si>
-  <si>
-    <t>38890+1443=40333/query</t>
-  </si>
-  <si>
-    <t>54s</t>
-  </si>
-  <si>
-    <t>36433+1389=37,822‬/query</t>
-  </si>
-  <si>
-    <t>65s</t>
-  </si>
-  <si>
-    <t>55132+1440=56,572‬/query</t>
+    <t>32192+1412=33,604‬‬/query</t>
   </si>
   <si>
     <t>Openviking实验数据（unagentic-learned）</t>
@@ -169,55 +154,46 @@
     <t>bot版本；0.2.10开发版；topk=5，relations不限制</t>
   </si>
   <si>
-    <t>6667+66=6,733/query</t>
-  </si>
-  <si>
-    <t>4324+98=4,422/query</t>
-  </si>
-  <si>
-    <t>5301+92=5,393/query</t>
-  </si>
-  <si>
-    <t>0.45s</t>
-  </si>
-  <si>
-    <t>7461+27=7,488/query</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>4514+159=4,673/query</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
-    <t>3333+56=3,389‬/query</t>
+    <t>9606+77=9,683‬</t>
+  </si>
+  <si>
+    <t>4528+99=4,627‬/query</t>
+  </si>
+  <si>
+    <t>7838+97=7,935/query</t>
+  </si>
+  <si>
+    <t>7223+34=7257</t>
+  </si>
+  <si>
+    <t>5675+162=5,837/query</t>
+  </si>
+  <si>
+    <t>4520+73=4593/query</t>
   </si>
   <si>
     <t>Openviking实验数据（unagentic-unlearned）</t>
   </si>
   <si>
-    <t>5384+54=5,438‬/query</t>
-  </si>
-  <si>
-    <t>3297+80=3,377/query</t>
+    <t>1.51s</t>
+  </si>
+  <si>
+    <t>5535+58=5,593</t>
+  </si>
+  <si>
+    <t>3293+77=3370/query</t>
   </si>
   <si>
     <t>3968+86=4,054‬/query</t>
   </si>
   <si>
-    <t>4778+23=4,801‬/query</t>
-  </si>
-  <si>
-    <t>4304+156=4460/query</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>3094+70=3,164‬/query</t>
+    <t>5726+27=5,753‬/query</t>
+  </si>
+  <si>
+    <t>4462+155=4,617/query</t>
+  </si>
+  <si>
+    <t>3972+73=4,045‬/query</t>
   </si>
 </sst>
 </file>
@@ -230,7 +206,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,6 +230,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -398,7 +380,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -413,7 +395,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor rgb="FF319B62"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="65"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -758,55 +746,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
@@ -821,74 +806,77 @@
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -901,11 +889,20 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1221,7 +1218,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26.875" customWidth="1"/>
@@ -1236,7 +1233,7 @@
     <col min="10" max="10" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1" spans="1:10">
+    <row r="1" ht="48" customHeight="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1267,182 +1264,208 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" ht="24.75" customHeight="1" spans="1:10">
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" ht="24.75" customHeight="1" spans="1:12">
       <c r="A2" s="1"/>
-      <c r="B2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>11</v>
+      <c r="B2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0.17</v>
-      </c>
-      <c r="F2" s="5">
+        <v>14</v>
+      </c>
+      <c r="E2" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="F2" s="6">
         <v>0</v>
       </c>
-      <c r="G2" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="G2" s="6">
+        <v>0.86</v>
+      </c>
+      <c r="H2" s="6">
+        <v>78</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="6">
+        <v>4.05</v>
+      </c>
+      <c r="K2" s="6">
+        <v>1.63</v>
+      </c>
+      <c r="L2" s="6">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
       <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0.16</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="H3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="E3" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="F3" s="6">
+        <v>9</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0.835</v>
+      </c>
+      <c r="H3" s="6">
+        <v>56</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="5">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="J3" s="6">
+        <v>3.63</v>
+      </c>
+      <c r="K3" s="6">
+        <v>1.3</v>
+      </c>
+      <c r="L3" s="6">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="5">
-        <v>0.22</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="E4" s="6">
+        <v>0.24</v>
+      </c>
+      <c r="F4" s="6">
         <v>0</v>
       </c>
-      <c r="G4" s="5">
-        <v>0.86</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="6">
+        <v>0.88</v>
+      </c>
+      <c r="H4" s="6">
+        <v>60</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="J4" s="6">
+        <v>3.69</v>
+      </c>
+      <c r="K4" s="6">
+        <v>1.34</v>
+      </c>
+      <c r="L4" s="6">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:12">
+      <c r="A5" s="1"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="5">
-        <v>3.86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+    </row>
+    <row r="6" ht="24" spans="1:12">
+      <c r="A6" s="1"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="5">
-        <v>0.14</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="E6" s="6">
+        <v>0.36</v>
+      </c>
+      <c r="F6" s="6">
         <v>0</v>
       </c>
-      <c r="G5" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="G6" s="6">
+        <v>0.92</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="5">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="6" ht="24" spans="1:10">
-      <c r="A6" s="1"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="2" t="s">
+      <c r="J6" s="6">
+        <v>3.22</v>
+      </c>
+      <c r="K6" s="6">
+        <v>1.06</v>
+      </c>
+      <c r="L6" s="6">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="1"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="5">
-        <v>0.36</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="E7" s="6">
+        <v>0.18</v>
+      </c>
+      <c r="F7" s="6">
         <v>0</v>
       </c>
-      <c r="G6" s="5">
-        <v>0.93</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="G7" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="5">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="2" t="s">
+      <c r="J7" s="6">
+        <v>3.54</v>
+      </c>
+      <c r="K7" s="6">
+        <v>1.42</v>
+      </c>
+      <c r="L7" s="6">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+    </row>
+    <row r="9" ht="48" customHeight="1" spans="1:12">
+      <c r="A9" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E7" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="5">
-        <v>4.59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-    </row>
-    <row r="9" ht="48" customHeight="1" spans="1:10">
-      <c r="A9" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>1</v>
@@ -1471,182 +1494,208 @@
       <c r="J9" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:10">
+      <c r="K9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:12">
       <c r="A10" s="1"/>
-      <c r="B10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>11</v>
+      <c r="B10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="F10" s="5">
+        <v>14</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="F10" s="6">
         <v>0</v>
       </c>
-      <c r="G10" s="5">
-        <v>0.82</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="G10" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" s="6">
+        <v>4.21</v>
+      </c>
+      <c r="K10" s="6">
+        <v>1.95</v>
+      </c>
+      <c r="L10" s="6">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="1"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.18</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0.835</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" s="5">
-        <v>5.53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="5">
-        <v>0.16</v>
-      </c>
-      <c r="F11" s="5">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="5">
-        <v>4.54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="J11" s="6">
+        <v>3.94</v>
+      </c>
+      <c r="K11" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="L11" s="6">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="1"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="6">
         <v>0.23</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="6">
         <v>0</v>
       </c>
-      <c r="G12" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="G12" s="6">
+        <v>0.81</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="6">
+        <v>4.05</v>
+      </c>
+      <c r="K12" s="6">
+        <v>1.56</v>
+      </c>
+      <c r="L12" s="6">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:12">
+      <c r="A13" s="1"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+    </row>
+    <row r="14" ht="24" spans="1:12">
+      <c r="A14" s="1"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.36</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="J14" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="K14" s="6">
+        <v>1.06</v>
+      </c>
+      <c r="L14" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="1"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.17</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J12" s="5">
-        <v>4.73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="1"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="5">
-        <v>0.16</v>
-      </c>
-      <c r="F13" s="5">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="I15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J13" s="5">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="14" ht="24" spans="1:10">
-      <c r="A14" s="1"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="F14" s="5">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5">
-        <v>0.93</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J14" s="5">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="1"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="5">
-        <v>0.14</v>
-      </c>
-      <c r="F15" s="5">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J15" s="5">
-        <v>4.73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
+      <c r="J15" s="6">
+        <v>4.25</v>
+      </c>
+      <c r="K15" s="6">
+        <v>2.02</v>
+      </c>
+      <c r="L15" s="6">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
     </row>
     <row r="17" ht="72" customHeight="1" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>1</v>
@@ -1673,184 +1722,184 @@
         <v>8</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:10">
       <c r="A18" s="1"/>
-      <c r="B18" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>11</v>
+      <c r="B18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="5">
+        <v>14</v>
+      </c>
+      <c r="E18" s="6">
         <v>0.21</v>
       </c>
-      <c r="F18" s="5">
-        <v>0.61</v>
-      </c>
-      <c r="G18" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="H18" s="5">
-        <v>2.14</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J18" s="5">
+      <c r="F18" s="6">
+        <v>0.71</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0.77</v>
+      </c>
+      <c r="H18" s="6">
+        <v>1.83</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J18" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="1"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
       <c r="D19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="5">
+        <v>16</v>
+      </c>
+      <c r="E19" s="6">
         <v>0.43</v>
       </c>
-      <c r="F19" s="5">
-        <v>0.93</v>
-      </c>
-      <c r="G19" s="5">
-        <v>0.88</v>
-      </c>
-      <c r="H19" s="5">
-        <v>0.92</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J19" s="5">
+      <c r="F19" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="G19" s="6">
+        <v>0.89</v>
+      </c>
+      <c r="H19" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="5">
-        <v>0.38</v>
-      </c>
-      <c r="F20" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="G20" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="H20" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="J20" s="5">
+      <c r="E20" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0.83</v>
+      </c>
+      <c r="H20" s="6">
+        <v>0.49</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J20" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="1"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
       <c r="D21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="5">
-        <v>0.41</v>
-      </c>
-      <c r="F21" s="5">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5">
-        <v>0.7325</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="J21" s="5">
+        <v>20</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.34</v>
+      </c>
+      <c r="F21" s="6">
+        <v>0.73</v>
+      </c>
+      <c r="G21" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="H21" s="6">
+        <v>0.53</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="22" ht="24" spans="1:10">
       <c r="A22" s="1"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
       <c r="D22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="5">
-        <v>0.38</v>
-      </c>
-      <c r="F22" s="5">
-        <v>0.96</v>
-      </c>
-      <c r="G22" s="5">
-        <v>0.92</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J22" s="5">
+        <v>21</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.36</v>
+      </c>
+      <c r="F22" s="6">
+        <v>0.94</v>
+      </c>
+      <c r="G22" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H22" s="6">
+        <v>0.47</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="1"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
       <c r="D23" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="5">
-        <v>0.29</v>
-      </c>
-      <c r="F23" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="G23" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J23" s="5">
+        <v>24</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.33</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="G23" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="H23" s="6">
+        <v>0.49</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
     </row>
     <row r="25" ht="72" customHeight="1" spans="1:10">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>1</v>
@@ -1877,166 +1926,166 @@
         <v>8</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" ht="24.75" customHeight="1" spans="1:10">
       <c r="A26" s="1"/>
-      <c r="B26" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>11</v>
+      <c r="B26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="F26" s="5">
-        <v>0.51</v>
-      </c>
-      <c r="G26" s="5">
-        <v>0.545</v>
-      </c>
-      <c r="H26" s="5">
-        <v>1.83</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J26" s="5">
+        <v>14</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0.56</v>
+      </c>
+      <c r="G26" s="6">
+        <v>0.61</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="J26" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="1"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
       <c r="D27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="5">
-        <v>0.38</v>
-      </c>
-      <c r="F27" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="G27" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="H27" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J27" s="5">
+        <v>16</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0.74</v>
+      </c>
+      <c r="G27" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="H27" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J27" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="1"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="5">
-        <v>0.29</v>
-      </c>
-      <c r="F28" s="5">
-        <v>0.63</v>
-      </c>
-      <c r="G28" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="H28" s="5">
-        <v>0.24</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J28" s="5">
+      <c r="E28" s="6">
+        <v>0.32</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="G28" s="6">
+        <v>0.61</v>
+      </c>
+      <c r="H28" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J28" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="1"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
       <c r="D29" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="5">
-        <v>0.29</v>
-      </c>
-      <c r="F29" s="5">
-        <v>0</v>
-      </c>
-      <c r="G29" s="5">
-        <v>0.63</v>
-      </c>
-      <c r="H29" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="J29" s="5">
+        <v>20</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.37</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="G29" s="6">
+        <v>0.64</v>
+      </c>
+      <c r="H29" s="6">
+        <v>0.31</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J29" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="24" spans="1:10">
       <c r="A30" s="1"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
       <c r="D30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="5">
-        <v>0.38</v>
-      </c>
-      <c r="F30" s="5">
-        <v>0.94</v>
-      </c>
-      <c r="G30" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="J30" s="5">
+        <v>21</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="F30" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="G30" s="6">
+        <v>0.89</v>
+      </c>
+      <c r="H30" s="6">
+        <v>0.34</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J30" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
       <c r="D31" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31" s="5">
-        <v>0.23</v>
-      </c>
-      <c r="F31" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="G31" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="J31" s="5">
+        <v>24</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0.79</v>
+      </c>
+      <c r="G31" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="H31" s="6">
+        <v>0.37</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J31" s="6">
         <v>1</v>
       </c>
     </row>

--- a/benchmark/RAG/figure/relations-figure.xlsx
+++ b/benchmark/RAG/figure/relations-figure.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="59">
   <si>
     <t>Openviking实验数据（agentic-learned)</t>
   </si>
@@ -94,6 +94,12 @@
     <t>LocoMo</t>
   </si>
   <si>
+    <t>37s</t>
+  </si>
+  <si>
+    <t>16848+982=17,830/query</t>
+  </si>
+  <si>
     <t>NaturalQuestions (NQ)</t>
   </si>
   <si>
@@ -131,6 +137,12 @@
   </si>
   <si>
     <t>25860+1809=27,669‬/query</t>
+  </si>
+  <si>
+    <t>43s</t>
+  </si>
+  <si>
+    <t>21280+1055=22,335/query</t>
   </si>
   <si>
     <t>50s</t>
@@ -206,7 +218,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,12 +240,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -380,7 +386,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -396,12 +402,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF319B62"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="65"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -746,52 +746,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
@@ -806,77 +809,74 @@
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -889,20 +889,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1264,208 +1255,224 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" ht="24.75" customHeight="1" spans="1:12">
       <c r="A2" s="1"/>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <v>0.2</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <v>0</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>0.86</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>78</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="5">
         <v>4.05</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>1.63</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="5">
         <v>1.36</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>0.19</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>9</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>0.835</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>56</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5">
         <v>3.63</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>1.3</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>1.25</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>0.24</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>0</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>0.88</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>60</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>3.69</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>1.34</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <v>1.28</v>
       </c>
     </row>
-    <row r="5" ht="16.5" spans="1:12">
+    <row r="5" spans="1:12">
       <c r="A5" s="1"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
+      <c r="E5" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0.83</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3.35</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1.26</v>
+      </c>
     </row>
     <row r="6" ht="24" spans="1:12">
       <c r="A6" s="1"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
       <c r="D6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="6">
+        <v>23</v>
+      </c>
+      <c r="E6" s="5">
         <v>0.36</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>0</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>0.92</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="6">
+      <c r="H6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="5">
         <v>3.22</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>1.06</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>0.98</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="6">
+        <v>26</v>
+      </c>
+      <c r="E7" s="5">
         <v>0.18</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>0</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>0.91</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="6">
+      <c r="H7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="5">
         <v>3.54</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>1.42</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>1.1</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>1</v>
@@ -1494,208 +1501,224 @@
       <c r="J9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:12">
       <c r="A10" s="1"/>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>0.19</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>0</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>0.85</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J10" s="6">
+      <c r="H10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="5">
         <v>4.21</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>1.95</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <v>1.33</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
       <c r="D11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>0.18</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <v>0</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>0.835</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="6">
+      <c r="H11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="5">
         <v>3.94</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <v>1.4</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="5">
         <v>1.27</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="1"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
       <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="5">
         <v>0.23</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>0</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>0.81</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" s="6">
+      <c r="H12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="5">
         <v>4.05</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <v>1.56</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <v>1.51</v>
       </c>
     </row>
-    <row r="13" ht="16.5" spans="1:12">
+    <row r="13" spans="1:12">
       <c r="A13" s="1"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
       <c r="D13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
+      <c r="E13" s="5">
+        <v>0.16</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.74</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="5">
+        <v>3.56</v>
+      </c>
+      <c r="K13" s="5">
+        <v>1.18</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1.17</v>
+      </c>
     </row>
     <row r="14" ht="24" spans="1:12">
       <c r="A14" s="1"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
       <c r="D14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="6">
+        <v>23</v>
+      </c>
+      <c r="E14" s="5">
         <v>0.36</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
         <v>0</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <v>0.9</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J14" s="6">
+      <c r="H14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14" s="5">
         <v>3.3</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>1.06</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="1"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
       <c r="D15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="6">
+        <v>26</v>
+      </c>
+      <c r="E15" s="5">
         <v>0.17</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
         <v>0</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <v>0.9</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J15" s="6">
+      <c r="H15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J15" s="5">
         <v>4.25</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <v>2.02</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="5">
         <v>1.22</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
     </row>
     <row r="17" ht="72" customHeight="1" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>1</v>
@@ -1722,184 +1745,184 @@
         <v>8</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:10">
       <c r="A18" s="1"/>
-      <c r="B18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="B18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="5">
         <v>0.21</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="5">
         <v>0.71</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="5">
         <v>0.77</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="5">
         <v>1.83</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J18" s="6">
+      <c r="I18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="1"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
       <c r="D19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="5">
         <v>0.43</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="5">
         <v>0.9</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="5">
         <v>0.89</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="5">
         <v>0.4</v>
       </c>
-      <c r="I19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J19" s="6">
+      <c r="I19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="5">
         <v>0.39</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="5">
         <v>0.9</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="5">
         <v>0.83</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="5">
         <v>0.49</v>
       </c>
-      <c r="I20" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J20" s="6">
+      <c r="I20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="1"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
       <c r="D21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="5">
         <v>0.34</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="5">
         <v>0.73</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="5">
         <v>0.7</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="5">
         <v>0.53</v>
       </c>
-      <c r="I21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J21" s="6">
+      <c r="I21" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J21" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="22" ht="24" spans="1:10">
       <c r="A22" s="1"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
       <c r="D22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="6">
+        <v>23</v>
+      </c>
+      <c r="E22" s="5">
         <v>0.36</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="5">
         <v>0.94</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="5">
         <v>0.9</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="5">
         <v>0.47</v>
       </c>
-      <c r="I22" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J22" s="6">
+      <c r="I22" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="1"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
       <c r="D23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="6">
+        <v>26</v>
+      </c>
+      <c r="E23" s="5">
         <v>0.33</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="5">
         <v>0.91</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="5">
         <v>0.85</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="5">
         <v>0.49</v>
       </c>
-      <c r="I23" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="J23" s="6">
+      <c r="I23" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J23" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
     </row>
     <row r="25" ht="72" customHeight="1" spans="1:10">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>1</v>
@@ -1926,166 +1949,166 @@
         <v>8</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" ht="24.75" customHeight="1" spans="1:10">
       <c r="A26" s="1"/>
-      <c r="B26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="B26" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="5">
         <v>0.16</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="5">
         <v>0.56</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="5">
         <v>0.61</v>
       </c>
-      <c r="H26" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J26" s="6">
+      <c r="H26" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J26" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="1"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
       <c r="D27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="5">
         <v>0.4</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="5">
         <v>0.74</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="5">
         <v>0.75</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="5">
         <v>0.3</v>
       </c>
-      <c r="I27" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J27" s="6">
+      <c r="I27" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="J27" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="1"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="5">
         <v>0.32</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="5">
         <v>0.67</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="5">
         <v>0.61</v>
       </c>
-      <c r="H28" s="6">
+      <c r="H28" s="5">
         <v>0.25</v>
       </c>
-      <c r="I28" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="J28" s="6">
+      <c r="I28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J28" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="1"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
       <c r="D29" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="5">
         <v>0.37</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="5">
         <v>0.7</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="5">
         <v>0.64</v>
       </c>
-      <c r="H29" s="6">
+      <c r="H29" s="5">
         <v>0.31</v>
       </c>
-      <c r="I29" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="J29" s="6">
+      <c r="I29" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="J29" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="24" spans="1:10">
       <c r="A30" s="1"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
       <c r="D30" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="6">
+        <v>23</v>
+      </c>
+      <c r="E30" s="5">
         <v>0.35</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="5">
         <v>0.93</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="5">
         <v>0.89</v>
       </c>
-      <c r="H30" s="6">
+      <c r="H30" s="5">
         <v>0.34</v>
       </c>
-      <c r="I30" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J30" s="6">
+      <c r="I30" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J30" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
       <c r="D31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="6">
+        <v>26</v>
+      </c>
+      <c r="E31" s="5">
         <v>0.22</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="5">
         <v>0.79</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="5">
         <v>0.7</v>
       </c>
-      <c r="H31" s="6">
+      <c r="H31" s="5">
         <v>0.37</v>
       </c>
-      <c r="I31" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J31" s="6">
+      <c r="I31" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J31" s="5">
         <v>1</v>
       </c>
     </row>
